--- a/controllers/relatorios/base/RELATORIO CONCRETAGEM.xlsx
+++ b/controllers/relatorios/base/RELATORIO CONCRETAGEM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lrone\SynologyDrive\fortanks_novo\controllers\relatorios\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180919E9-F1CE-4330-BAD0-F5CD2B29B582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F5DFAA5-9A4C-4B38-B536-2E452E86D532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" tabRatio="866" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,8 @@
     <sheet name="1" sheetId="1492" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'1'!$A$1:$S$54</definedName>
-    <definedName name="Print_Area" localSheetId="0">'1'!$A$1:$S$54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'1'!$B$1:$V$56</definedName>
+    <definedName name="Print_Area" localSheetId="0">'1'!$C$2:$U$55</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1726,197 +1726,145 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1936,9 +1884,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1953,111 +1901,163 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2103,9 +2103,9 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="504825" cy="847725"/>
@@ -2141,9 +2141,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="523875" cy="857250"/>
@@ -2179,9 +2179,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="523875" cy="838200"/>
@@ -2217,9 +2217,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="533400" cy="847725"/>
@@ -2255,9 +2255,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>47627</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>24492</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="495300" cy="847725"/>
@@ -2293,9 +2293,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1533525" cy="542925"/>
@@ -2331,16 +2331,16 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>321131</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>5443</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>594472</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>226088</xdr:rowOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>598</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2375,15 +2375,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>21774</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>191051</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>304801</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>287433</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2714,1586 +2714,1588 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E298753-E8F2-4F7B-BB20-4B28F4B1BB3D}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T101"/>
+  <dimension ref="C1:V102"/>
   <sheetFormatPr defaultColWidth="14.3828125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.53515625" customWidth="1"/>
-    <col min="2" max="2" width="9.84375" customWidth="1"/>
-    <col min="3" max="3" width="3.15234375" customWidth="1"/>
-    <col min="4" max="4" width="8.69140625" customWidth="1"/>
-    <col min="5" max="5" width="7.3828125" customWidth="1"/>
-    <col min="6" max="6" width="1" customWidth="1"/>
-    <col min="7" max="7" width="0.84375" customWidth="1"/>
-    <col min="8" max="8" width="1.3046875" customWidth="1"/>
-    <col min="9" max="9" width="2.3828125" customWidth="1"/>
-    <col min="10" max="10" width="8.3046875" customWidth="1"/>
-    <col min="11" max="12" width="5.3046875" customWidth="1"/>
-    <col min="13" max="13" width="4.69140625" customWidth="1"/>
-    <col min="14" max="14" width="6.15234375" customWidth="1"/>
-    <col min="15" max="15" width="9.69140625" customWidth="1"/>
-    <col min="16" max="16" width="4.69140625" customWidth="1"/>
-    <col min="17" max="17" width="5.3046875" customWidth="1"/>
-    <col min="18" max="19" width="8.69140625" customWidth="1"/>
-    <col min="20" max="20" width="1.84375" customWidth="1"/>
+    <col min="2" max="2" width="2" customWidth="1"/>
+    <col min="3" max="3" width="9.53515625" customWidth="1"/>
+    <col min="4" max="4" width="9.84375" customWidth="1"/>
+    <col min="5" max="5" width="3.15234375" customWidth="1"/>
+    <col min="6" max="6" width="8.69140625" customWidth="1"/>
+    <col min="7" max="7" width="7.3828125" customWidth="1"/>
+    <col min="8" max="8" width="1" customWidth="1"/>
+    <col min="9" max="9" width="0.84375" customWidth="1"/>
+    <col min="10" max="10" width="1.3046875" customWidth="1"/>
+    <col min="11" max="11" width="2.3828125" customWidth="1"/>
+    <col min="12" max="12" width="8.3046875" customWidth="1"/>
+    <col min="13" max="14" width="5.3046875" customWidth="1"/>
+    <col min="15" max="15" width="4.69140625" customWidth="1"/>
+    <col min="16" max="16" width="6.15234375" customWidth="1"/>
+    <col min="17" max="17" width="9.69140625" customWidth="1"/>
+    <col min="18" max="18" width="4.69140625" customWidth="1"/>
+    <col min="19" max="19" width="5.3046875" customWidth="1"/>
+    <col min="20" max="21" width="8.69140625" customWidth="1"/>
+    <col min="22" max="22" width="1.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="69"/>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="78" t="s">
+    <row r="1" spans="3:22" ht="9.4499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C2" s="201"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="202" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="80"/>
-      <c r="P1" s="78" t="s">
+      <c r="H2" s="106"/>
+      <c r="I2" s="106"/>
+      <c r="J2" s="106"/>
+      <c r="K2" s="106"/>
+      <c r="L2" s="106"/>
+      <c r="M2" s="106"/>
+      <c r="N2" s="106"/>
+      <c r="O2" s="106"/>
+      <c r="P2" s="106"/>
+      <c r="Q2" s="203"/>
+      <c r="R2" s="202" t="s">
         <v>1</v>
       </c>
-      <c r="Q1" s="79"/>
-      <c r="R1" s="81" t="s">
+      <c r="S2" s="106"/>
+      <c r="T2" s="204" t="s">
         <v>89</v>
       </c>
-      <c r="S1" s="82"/>
-    </row>
-    <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="83" t="s">
+      <c r="U2" s="205"/>
+    </row>
+    <row r="3" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C3" s="123"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="144"/>
+      <c r="G3" s="206" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="85" t="s">
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="207" t="s">
         <v>90</v>
       </c>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="84"/>
-      <c r="O2" s="84"/>
-      <c r="P2" s="84"/>
-      <c r="Q2" s="84"/>
-      <c r="R2" s="84"/>
-      <c r="S2" s="86"/>
-    </row>
-    <row r="3" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="75"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="87" t="s">
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="92"/>
+    </row>
+    <row r="4" spans="3:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C4" s="104"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="208" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="88" t="s">
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="209" t="s">
         <v>91</v>
       </c>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
-      <c r="K3" s="76"/>
-      <c r="L3" s="76"/>
-      <c r="M3" s="76"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="89"/>
-    </row>
-    <row r="4" spans="1:20" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-    </row>
-    <row r="5" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="107" t="s">
+      <c r="K4" s="78"/>
+      <c r="L4" s="78"/>
+      <c r="M4" s="78"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="86"/>
+    </row>
+    <row r="5" spans="3:22" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+    </row>
+    <row r="6" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C6" s="193" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="108"/>
-      <c r="C5" s="108"/>
-      <c r="D5" s="108"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="108"/>
-      <c r="H5" s="108"/>
-      <c r="I5" s="108"/>
-      <c r="J5" s="108"/>
-      <c r="K5" s="108"/>
-      <c r="L5" s="108"/>
-      <c r="M5" s="109"/>
-      <c r="N5" s="109"/>
-      <c r="O5" s="109"/>
-      <c r="P5" s="109"/>
-      <c r="Q5" s="109"/>
-      <c r="R5" s="108"/>
-      <c r="S5" s="110"/>
-    </row>
-    <row r="6" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="61" t="s">
+      <c r="D6" s="194"/>
+      <c r="E6" s="194"/>
+      <c r="F6" s="194"/>
+      <c r="G6" s="194"/>
+      <c r="H6" s="194"/>
+      <c r="I6" s="194"/>
+      <c r="J6" s="194"/>
+      <c r="K6" s="194"/>
+      <c r="L6" s="194"/>
+      <c r="M6" s="194"/>
+      <c r="N6" s="194"/>
+      <c r="O6" s="219"/>
+      <c r="P6" s="219"/>
+      <c r="Q6" s="219"/>
+      <c r="R6" s="219"/>
+      <c r="S6" s="219"/>
+      <c r="T6" s="194"/>
+      <c r="U6" s="195"/>
+    </row>
+    <row r="7" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C7" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="111" t="s">
+      <c r="D7" s="5"/>
+      <c r="E7" s="220" t="s">
         <v>78</v>
       </c>
-      <c r="D6" s="112"/>
-      <c r="E6" s="113" t="s">
+      <c r="F7" s="109"/>
+      <c r="G7" s="221" t="s">
         <v>92</v>
       </c>
-      <c r="F6" s="114"/>
-      <c r="G6" s="114"/>
-      <c r="H6" s="114"/>
-      <c r="I6" s="114"/>
-      <c r="J6" s="4" t="s">
+      <c r="H7" s="222"/>
+      <c r="I7" s="222"/>
+      <c r="J7" s="222"/>
+      <c r="K7" s="222"/>
+      <c r="L7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="M7" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="L6" s="4"/>
-      <c r="M6" s="43" t="s">
+      <c r="N7" s="4"/>
+      <c r="O7" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="N6" s="44"/>
-      <c r="O6" s="59" t="s">
+      <c r="P7" s="44"/>
+      <c r="Q7" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="P6" s="44"/>
-      <c r="Q6" s="45"/>
-      <c r="R6" s="41" t="s">
+      <c r="R7" s="44"/>
+      <c r="S7" s="45"/>
+      <c r="T7" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="S6" s="67" t="s">
+      <c r="U7" s="67" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="115" t="s">
+    <row r="8" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C8" s="177" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="95"/>
-      <c r="C7" s="94" t="s">
+      <c r="D8" s="170"/>
+      <c r="E8" s="175" t="s">
         <v>78</v>
       </c>
-      <c r="D7" s="84"/>
-      <c r="E7" s="113" t="s">
+      <c r="F8" s="88"/>
+      <c r="G8" s="221" t="s">
         <v>95</v>
       </c>
-      <c r="F7" s="114"/>
-      <c r="G7" s="114"/>
-      <c r="H7" s="114"/>
-      <c r="I7" s="114"/>
-      <c r="J7" s="4" t="s">
+      <c r="H8" s="222"/>
+      <c r="I8" s="222"/>
+      <c r="J8" s="222"/>
+      <c r="K8" s="222"/>
+      <c r="L8" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="42" t="s">
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="97" t="s">
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="210" t="s">
         <v>96</v>
       </c>
-      <c r="Q7" s="98"/>
-      <c r="R7" s="99"/>
-      <c r="S7" s="100"/>
-    </row>
-    <row r="8" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="90" t="s">
+      <c r="S8" s="211"/>
+      <c r="T8" s="212"/>
+      <c r="U8" s="213"/>
+    </row>
+    <row r="9" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C9" s="182" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="91"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="3" t="s">
+      <c r="D9" s="116"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="48"/>
-      <c r="F8" s="94"/>
-      <c r="G8" s="84"/>
-      <c r="H8" s="84"/>
-      <c r="I8" s="84"/>
-      <c r="J8" s="46"/>
-      <c r="K8" s="95" t="s">
+      <c r="G9" s="48"/>
+      <c r="H9" s="175"/>
+      <c r="I9" s="88"/>
+      <c r="J9" s="88"/>
+      <c r="K9" s="88"/>
+      <c r="L9" s="46"/>
+      <c r="M9" s="170" t="s">
         <v>9</v>
       </c>
-      <c r="L8" s="96"/>
-      <c r="M8" s="5" t="s">
+      <c r="N9" s="89"/>
+      <c r="O9" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="97" t="s">
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="210" t="s">
         <v>97</v>
       </c>
-      <c r="Q8" s="98"/>
-      <c r="R8" s="99"/>
-      <c r="S8" s="100"/>
-      <c r="T8" s="1"/>
-    </row>
-    <row r="9" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="92"/>
-      <c r="B9" s="93"/>
-      <c r="C9" s="7" t="s">
+      <c r="S9" s="211"/>
+      <c r="T9" s="212"/>
+      <c r="U9" s="213"/>
+      <c r="V9" s="1"/>
+    </row>
+    <row r="10" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C10" s="183"/>
+      <c r="D10" s="110"/>
+      <c r="E10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="F10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="101" t="s">
+      <c r="G10" s="126" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="84"/>
-      <c r="G9" s="84"/>
-      <c r="H9" s="84"/>
-      <c r="I9" s="84"/>
-      <c r="J9" s="84"/>
-      <c r="K9" s="95" t="s">
+      <c r="H10" s="88"/>
+      <c r="I10" s="88"/>
+      <c r="J10" s="88"/>
+      <c r="K10" s="88"/>
+      <c r="L10" s="88"/>
+      <c r="M10" s="170" t="s">
         <v>9</v>
       </c>
-      <c r="L9" s="96"/>
-      <c r="M9" s="102" t="s">
+      <c r="N10" s="89"/>
+      <c r="O10" s="214" t="s">
         <v>10</v>
       </c>
-      <c r="N9" s="103"/>
-      <c r="O9" s="103"/>
-      <c r="P9" s="104"/>
-      <c r="Q9" s="103"/>
-      <c r="R9" s="105" t="s">
+      <c r="P10" s="215"/>
+      <c r="Q10" s="215"/>
+      <c r="R10" s="216"/>
+      <c r="S10" s="215"/>
+      <c r="T10" s="217" t="s">
         <v>75</v>
       </c>
-      <c r="S9" s="106"/>
-      <c r="T9" s="1"/>
-    </row>
-    <row r="10" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="63" t="s">
+      <c r="U10" s="218"/>
+      <c r="V10" s="1"/>
+    </row>
+    <row r="11" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C11" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="116" t="s">
+      <c r="D11" s="187" t="s">
         <v>98</v>
       </c>
-      <c r="C10" s="117"/>
-      <c r="D10" s="117"/>
-      <c r="E10" s="117"/>
-      <c r="F10" s="117"/>
-      <c r="G10" s="117"/>
-      <c r="H10" s="117"/>
-      <c r="I10" s="118"/>
-      <c r="J10" s="119" t="s">
+      <c r="E11" s="188"/>
+      <c r="F11" s="188"/>
+      <c r="G11" s="188"/>
+      <c r="H11" s="188"/>
+      <c r="I11" s="188"/>
+      <c r="J11" s="188"/>
+      <c r="K11" s="189"/>
+      <c r="L11" s="190" t="s">
         <v>15</v>
       </c>
-      <c r="K10" s="84"/>
-      <c r="L10" s="84"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="10" t="s">
+      <c r="M11" s="88"/>
+      <c r="N11" s="88"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="10"/>
-      <c r="P10" s="60" t="s">
+      <c r="Q11" s="10"/>
+      <c r="R11" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="Q10" s="95" t="s">
+      <c r="S11" s="170" t="s">
         <v>17</v>
       </c>
-      <c r="R10" s="84"/>
-      <c r="S10" s="120"/>
-      <c r="T10" s="1"/>
-    </row>
-    <row r="11" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="64" t="s">
+      <c r="T11" s="88"/>
+      <c r="U11" s="191"/>
+      <c r="V11" s="1"/>
+    </row>
+    <row r="12" spans="3:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C12" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="121" t="s">
+      <c r="D12" s="166" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="122"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="122"/>
-      <c r="F11" s="122"/>
-      <c r="G11" s="122"/>
-      <c r="H11" s="122"/>
-      <c r="I11" s="122"/>
-      <c r="J11" s="122"/>
-      <c r="K11" s="122"/>
-      <c r="L11" s="122"/>
-      <c r="M11" s="122"/>
-      <c r="N11" s="122"/>
-      <c r="O11" s="122"/>
-      <c r="P11" s="123"/>
-      <c r="Q11" s="122"/>
-      <c r="R11" s="122"/>
-      <c r="S11" s="124"/>
-      <c r="T11" s="1"/>
-    </row>
-    <row r="12" spans="1:20" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-    </row>
-    <row r="13" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="107" t="s">
+      <c r="E12" s="165"/>
+      <c r="F12" s="165"/>
+      <c r="G12" s="165"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="165"/>
+      <c r="J12" s="165"/>
+      <c r="K12" s="165"/>
+      <c r="L12" s="165"/>
+      <c r="M12" s="165"/>
+      <c r="N12" s="165"/>
+      <c r="O12" s="165"/>
+      <c r="P12" s="165"/>
+      <c r="Q12" s="165"/>
+      <c r="R12" s="162"/>
+      <c r="S12" s="165"/>
+      <c r="T12" s="165"/>
+      <c r="U12" s="192"/>
+      <c r="V12" s="1"/>
+    </row>
+    <row r="13" spans="3:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+    </row>
+    <row r="14" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C14" s="193" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="108"/>
-      <c r="C13" s="108"/>
-      <c r="D13" s="108"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="108"/>
-      <c r="H13" s="108"/>
-      <c r="I13" s="108"/>
-      <c r="J13" s="108"/>
-      <c r="K13" s="108"/>
-      <c r="L13" s="108"/>
-      <c r="M13" s="108"/>
-      <c r="N13" s="108"/>
-      <c r="O13" s="108"/>
-      <c r="P13" s="108"/>
-      <c r="Q13" s="108"/>
-      <c r="R13" s="108"/>
-      <c r="S13" s="110"/>
-    </row>
-    <row r="14" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="62" t="s">
+      <c r="D14" s="194"/>
+      <c r="E14" s="194"/>
+      <c r="F14" s="194"/>
+      <c r="G14" s="194"/>
+      <c r="H14" s="194"/>
+      <c r="I14" s="194"/>
+      <c r="J14" s="194"/>
+      <c r="K14" s="194"/>
+      <c r="L14" s="194"/>
+      <c r="M14" s="194"/>
+      <c r="N14" s="194"/>
+      <c r="O14" s="194"/>
+      <c r="P14" s="194"/>
+      <c r="Q14" s="194"/>
+      <c r="R14" s="194"/>
+      <c r="S14" s="194"/>
+      <c r="T14" s="194"/>
+      <c r="U14" s="195"/>
+    </row>
+    <row r="15" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C15" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="51"/>
-      <c r="C14" s="125" t="s">
+      <c r="D15" s="51"/>
+      <c r="E15" s="196" t="s">
         <v>99</v>
       </c>
-      <c r="D14" s="117"/>
-      <c r="E14" s="117"/>
-      <c r="F14" s="126" t="s">
+      <c r="F15" s="188"/>
+      <c r="G15" s="188"/>
+      <c r="H15" s="197" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="84"/>
-      <c r="H14" s="84"/>
-      <c r="I14" s="84"/>
-      <c r="J14" s="127" t="s">
+      <c r="I15" s="88"/>
+      <c r="J15" s="88"/>
+      <c r="K15" s="88"/>
+      <c r="L15" s="198" t="s">
         <v>100</v>
       </c>
-      <c r="K14" s="117"/>
-      <c r="L14" s="118"/>
-      <c r="M14" s="11" t="s">
+      <c r="M15" s="188"/>
+      <c r="N15" s="189"/>
+      <c r="O15" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N14" s="50"/>
-      <c r="O14" s="49"/>
-      <c r="P14" s="49"/>
-      <c r="Q14" s="49"/>
-      <c r="R14" s="128" t="s">
+      <c r="P15" s="50"/>
+      <c r="Q15" s="49"/>
+      <c r="R15" s="49"/>
+      <c r="S15" s="49"/>
+      <c r="T15" s="199" t="s">
         <v>101</v>
       </c>
-      <c r="S14" s="129"/>
-      <c r="T14" s="1"/>
-    </row>
-    <row r="15" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="115" t="s">
+      <c r="U15" s="200"/>
+      <c r="V15" s="1"/>
+    </row>
+    <row r="16" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C16" s="177" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="84"/>
-      <c r="C15" s="130" t="s">
+      <c r="D16" s="88"/>
+      <c r="E16" s="178" t="s">
         <v>102</v>
       </c>
-      <c r="D15" s="131"/>
-      <c r="E15" s="132"/>
-      <c r="F15" s="95" t="s">
+      <c r="F16" s="179"/>
+      <c r="G16" s="180"/>
+      <c r="H16" s="170" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="84"/>
-      <c r="H15" s="84"/>
-      <c r="I15" s="84"/>
-      <c r="J15" s="84"/>
-      <c r="K15" s="84"/>
-      <c r="L15" s="84"/>
-      <c r="M15" s="133" t="s">
+      <c r="I16" s="88"/>
+      <c r="J16" s="88"/>
+      <c r="K16" s="88"/>
+      <c r="L16" s="88"/>
+      <c r="M16" s="88"/>
+      <c r="N16" s="88"/>
+      <c r="O16" s="181" t="s">
         <v>103</v>
       </c>
-      <c r="N15" s="96"/>
-      <c r="O15" s="101" t="s">
+      <c r="P16" s="89"/>
+      <c r="Q16" s="126" t="s">
         <v>25</v>
       </c>
-      <c r="P15" s="84"/>
-      <c r="Q15" s="84"/>
-      <c r="R15" s="84"/>
-      <c r="S15" s="65" t="s">
+      <c r="R16" s="88"/>
+      <c r="S16" s="88"/>
+      <c r="T16" s="88"/>
+      <c r="U16" s="65" t="s">
         <v>104</v>
       </c>
-      <c r="T15" s="1"/>
-    </row>
-    <row r="16" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="90" t="s">
+      <c r="V16" s="1"/>
+    </row>
+    <row r="17" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C17" s="182" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="91"/>
-      <c r="C16" s="6" t="s">
+      <c r="D17" s="116"/>
+      <c r="E17" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="F17" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="134" t="s">
+      <c r="G17" s="184" t="s">
         <v>106</v>
       </c>
-      <c r="F16" s="135"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135"/>
-      <c r="I16" s="135"/>
-      <c r="J16" s="135"/>
-      <c r="K16" s="136" t="s">
+      <c r="H17" s="185"/>
+      <c r="I17" s="185"/>
+      <c r="J17" s="185"/>
+      <c r="K17" s="185"/>
+      <c r="L17" s="185"/>
+      <c r="M17" s="186" t="s">
         <v>9</v>
       </c>
-      <c r="L16" s="93"/>
-      <c r="M16" s="13" t="s">
+      <c r="N17" s="110"/>
+      <c r="O17" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="N16" s="50"/>
-      <c r="O16" s="136" t="s">
+      <c r="P17" s="50"/>
+      <c r="Q17" s="186" t="s">
         <v>87</v>
       </c>
-      <c r="P16" s="112"/>
-      <c r="Q16" s="112"/>
-      <c r="R16" s="112"/>
-      <c r="S16" s="137"/>
-      <c r="T16" s="14"/>
-    </row>
-    <row r="17" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="92"/>
-      <c r="B17" s="93"/>
-      <c r="C17" s="6" t="s">
+      <c r="R17" s="109"/>
+      <c r="S17" s="109"/>
+      <c r="T17" s="109"/>
+      <c r="U17" s="174"/>
+      <c r="V17" s="14"/>
+    </row>
+    <row r="18" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C18" s="183"/>
+      <c r="D18" s="110"/>
+      <c r="E18" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="F18" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="134" t="s">
+      <c r="G18" s="184" t="s">
         <v>108</v>
       </c>
-      <c r="F17" s="135"/>
-      <c r="G17" s="135"/>
-      <c r="H17" s="135"/>
-      <c r="I17" s="135"/>
-      <c r="J17" s="135"/>
-      <c r="K17" s="95" t="s">
+      <c r="H18" s="185"/>
+      <c r="I18" s="185"/>
+      <c r="J18" s="185"/>
+      <c r="K18" s="185"/>
+      <c r="L18" s="185"/>
+      <c r="M18" s="170" t="s">
         <v>9</v>
       </c>
-      <c r="L17" s="96"/>
-      <c r="M17" s="53" t="s">
+      <c r="N18" s="89"/>
+      <c r="O18" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="N17" s="54"/>
-      <c r="O17" s="54"/>
-      <c r="P17" s="54"/>
-      <c r="Q17" s="54"/>
-      <c r="R17" s="150"/>
-      <c r="S17" s="151"/>
-      <c r="T17" s="14"/>
-    </row>
-    <row r="18" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="152" t="s">
+      <c r="P18" s="54"/>
+      <c r="Q18" s="54"/>
+      <c r="R18" s="54"/>
+      <c r="S18" s="54"/>
+      <c r="T18" s="171"/>
+      <c r="U18" s="172"/>
+      <c r="V18" s="14"/>
+    </row>
+    <row r="19" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C19" s="173" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="73"/>
-      <c r="C18" s="73"/>
-      <c r="D18" s="73"/>
-      <c r="E18" s="73"/>
-      <c r="F18" s="73"/>
-      <c r="G18" s="73"/>
-      <c r="H18" s="73"/>
-      <c r="I18" s="73"/>
-      <c r="J18" s="73"/>
-      <c r="K18" s="73"/>
-      <c r="L18" s="74"/>
-      <c r="M18" s="140"/>
-      <c r="N18" s="73"/>
-      <c r="O18" s="73"/>
-      <c r="P18" s="73"/>
-      <c r="Q18" s="73"/>
-      <c r="R18" s="73"/>
-      <c r="S18" s="141"/>
-      <c r="T18" s="14"/>
-    </row>
-    <row r="19" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="152" t="s">
+      <c r="D19" s="159"/>
+      <c r="E19" s="159"/>
+      <c r="F19" s="159"/>
+      <c r="G19" s="159"/>
+      <c r="H19" s="159"/>
+      <c r="I19" s="159"/>
+      <c r="J19" s="159"/>
+      <c r="K19" s="159"/>
+      <c r="L19" s="159"/>
+      <c r="M19" s="159"/>
+      <c r="N19" s="144"/>
+      <c r="O19" s="158"/>
+      <c r="P19" s="159"/>
+      <c r="Q19" s="159"/>
+      <c r="R19" s="159"/>
+      <c r="S19" s="159"/>
+      <c r="T19" s="159"/>
+      <c r="U19" s="160"/>
+      <c r="V19" s="14"/>
+    </row>
+    <row r="20" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C20" s="173" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="73"/>
-      <c r="C19" s="74"/>
-      <c r="D19" s="58" t="s">
+      <c r="D20" s="159"/>
+      <c r="E20" s="144"/>
+      <c r="F20" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="G20" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="L19" s="16"/>
-      <c r="M19" s="153"/>
-      <c r="N19" s="73"/>
-      <c r="O19" s="73"/>
-      <c r="P19" s="73"/>
-      <c r="Q19" s="73"/>
-      <c r="R19" s="73"/>
-      <c r="S19" s="141"/>
-      <c r="T19" s="14"/>
-    </row>
-    <row r="20" spans="1:20" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="66"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
       <c r="H20" s="16"/>
       <c r="I20" s="16"/>
-      <c r="J20" s="47"/>
+      <c r="J20" s="16"/>
       <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="154"/>
-      <c r="N20" s="112"/>
-      <c r="O20" s="112"/>
-      <c r="P20" s="112"/>
-      <c r="Q20" s="112"/>
-      <c r="R20" s="112"/>
-      <c r="S20" s="137"/>
-      <c r="T20" s="14"/>
-    </row>
-    <row r="21" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="62" t="s">
+      <c r="L20" s="9"/>
+      <c r="M20" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="N20" s="16"/>
+      <c r="O20" s="143"/>
+      <c r="P20" s="159"/>
+      <c r="Q20" s="159"/>
+      <c r="R20" s="159"/>
+      <c r="S20" s="159"/>
+      <c r="T20" s="159"/>
+      <c r="U20" s="160"/>
+      <c r="V20" s="14"/>
+    </row>
+    <row r="21" spans="3:22" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C21" s="66"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="47"/>
+      <c r="M21" s="16"/>
+      <c r="N21" s="16"/>
+      <c r="O21" s="145"/>
+      <c r="P21" s="109"/>
+      <c r="Q21" s="109"/>
+      <c r="R21" s="109"/>
+      <c r="S21" s="109"/>
+      <c r="T21" s="109"/>
+      <c r="U21" s="174"/>
+      <c r="V21" s="14"/>
+    </row>
+    <row r="22" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C22" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="47"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="52" t="s">
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="52" t="s">
         <v>109</v>
       </c>
-      <c r="E21" s="94" t="s">
+      <c r="G22" s="175" t="s">
         <v>34</v>
       </c>
-      <c r="F21" s="84"/>
-      <c r="G21" s="155" t="s">
+      <c r="H22" s="88"/>
+      <c r="I22" s="176" t="s">
         <v>110</v>
       </c>
-      <c r="H21" s="84"/>
-      <c r="I21" s="84"/>
-      <c r="J21" s="84"/>
-      <c r="K21" s="10" t="s">
+      <c r="J22" s="88"/>
+      <c r="K22" s="88"/>
+      <c r="L22" s="88"/>
+      <c r="M22" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="L21" s="17"/>
-      <c r="M21" s="53" t="s">
+      <c r="N22" s="17"/>
+      <c r="O22" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="N21" s="54"/>
-      <c r="O21" s="150"/>
-      <c r="P21" s="139"/>
-      <c r="Q21" s="139"/>
-      <c r="R21" s="139"/>
-      <c r="S21" s="151"/>
-    </row>
-    <row r="22" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="62" t="s">
+      <c r="P22" s="54"/>
+      <c r="Q22" s="171"/>
+      <c r="R22" s="102"/>
+      <c r="S22" s="102"/>
+      <c r="T22" s="102"/>
+      <c r="U22" s="172"/>
+    </row>
+    <row r="23" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C23" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="47" t="str">
-        <f>IF(R1="","",R1)</f>
+      <c r="D23" s="47" t="str">
+        <f>IF(T2="","",T2)</f>
         <v>{1}</v>
       </c>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="138" t="s">
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="157" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="139"/>
-      <c r="G22" s="139"/>
-      <c r="H22" s="139"/>
-      <c r="I22" s="139"/>
-      <c r="J22" s="139"/>
-      <c r="K22" s="139"/>
-      <c r="L22" s="91"/>
-      <c r="M22" s="140" t="s">
+      <c r="H23" s="102"/>
+      <c r="I23" s="102"/>
+      <c r="J23" s="102"/>
+      <c r="K23" s="102"/>
+      <c r="L23" s="102"/>
+      <c r="M23" s="102"/>
+      <c r="N23" s="116"/>
+      <c r="O23" s="158" t="s">
         <v>39</v>
       </c>
-      <c r="N22" s="73"/>
-      <c r="O22" s="73"/>
-      <c r="P22" s="73"/>
-      <c r="Q22" s="73"/>
-      <c r="R22" s="73"/>
-      <c r="S22" s="141"/>
-    </row>
-    <row r="23" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="144" t="s">
+      <c r="P23" s="159"/>
+      <c r="Q23" s="159"/>
+      <c r="R23" s="159"/>
+      <c r="S23" s="159"/>
+      <c r="T23" s="159"/>
+      <c r="U23" s="160"/>
+    </row>
+    <row r="24" spans="3:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C24" s="164" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="122"/>
-      <c r="C23" s="121">
+      <c r="D24" s="165"/>
+      <c r="E24" s="166">
         <v>4</v>
       </c>
-      <c r="D23" s="145"/>
-      <c r="E23" s="146" t="s">
+      <c r="F24" s="167"/>
+      <c r="G24" s="168" t="s">
         <v>41</v>
       </c>
-      <c r="F23" s="123"/>
-      <c r="G23" s="123"/>
-      <c r="H23" s="123"/>
-      <c r="I23" s="123"/>
-      <c r="J23" s="123"/>
-      <c r="K23" s="123"/>
-      <c r="L23" s="147"/>
-      <c r="M23" s="142"/>
-      <c r="N23" s="123"/>
-      <c r="O23" s="123"/>
-      <c r="P23" s="123"/>
-      <c r="Q23" s="123"/>
-      <c r="R23" s="123"/>
-      <c r="S23" s="143"/>
-    </row>
-    <row r="24" spans="1:20" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="39"/>
-      <c r="S24" s="2"/>
-    </row>
-    <row r="25" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="148" t="s">
+      <c r="H24" s="162"/>
+      <c r="I24" s="162"/>
+      <c r="J24" s="162"/>
+      <c r="K24" s="162"/>
+      <c r="L24" s="162"/>
+      <c r="M24" s="162"/>
+      <c r="N24" s="169"/>
+      <c r="O24" s="161"/>
+      <c r="P24" s="162"/>
+      <c r="Q24" s="162"/>
+      <c r="R24" s="162"/>
+      <c r="S24" s="162"/>
+      <c r="T24" s="162"/>
+      <c r="U24" s="163"/>
+    </row>
+    <row r="25" spans="3:22" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="39"/>
+      <c r="U25" s="2"/>
+    </row>
+    <row r="26" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C26" s="105" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="79"/>
-      <c r="C25" s="79"/>
-      <c r="D25" s="79"/>
-      <c r="E25" s="79"/>
-      <c r="F25" s="79"/>
-      <c r="G25" s="79"/>
-      <c r="H25" s="79"/>
-      <c r="I25" s="79"/>
-      <c r="J25" s="79"/>
-      <c r="K25" s="79"/>
-      <c r="L25" s="79"/>
-      <c r="M25" s="79"/>
-      <c r="N25" s="79"/>
-      <c r="O25" s="79"/>
-      <c r="P25" s="79"/>
-      <c r="Q25" s="79"/>
-      <c r="R25" s="79"/>
-      <c r="S25" s="149"/>
-    </row>
-    <row r="26" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="161" t="s">
+      <c r="D26" s="106"/>
+      <c r="E26" s="106"/>
+      <c r="F26" s="106"/>
+      <c r="G26" s="106"/>
+      <c r="H26" s="106"/>
+      <c r="I26" s="106"/>
+      <c r="J26" s="106"/>
+      <c r="K26" s="106"/>
+      <c r="L26" s="106"/>
+      <c r="M26" s="106"/>
+      <c r="N26" s="106"/>
+      <c r="O26" s="106"/>
+      <c r="P26" s="106"/>
+      <c r="Q26" s="106"/>
+      <c r="R26" s="106"/>
+      <c r="S26" s="106"/>
+      <c r="T26" s="106"/>
+      <c r="U26" s="107"/>
+    </row>
+    <row r="27" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C27" s="131" t="s">
         <v>111</v>
       </c>
-      <c r="B26" s="162"/>
-      <c r="C26" s="162"/>
-      <c r="D26" s="162"/>
-      <c r="E26" s="162"/>
-      <c r="F26" s="162"/>
-      <c r="G26" s="162"/>
-      <c r="H26" s="162"/>
-      <c r="I26" s="162"/>
-      <c r="J26" s="162"/>
-      <c r="K26" s="162"/>
-      <c r="L26" s="162"/>
-      <c r="M26" s="162"/>
-      <c r="N26" s="162"/>
-      <c r="O26" s="162"/>
-      <c r="P26" s="162"/>
-      <c r="Q26" s="162"/>
-      <c r="R26" s="162"/>
-      <c r="S26" s="163"/>
-    </row>
-    <row r="27" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="164"/>
-      <c r="B27" s="165"/>
-      <c r="C27" s="165"/>
-      <c r="D27" s="165"/>
-      <c r="E27" s="165"/>
-      <c r="F27" s="165"/>
-      <c r="G27" s="165"/>
-      <c r="H27" s="165"/>
-      <c r="I27" s="165"/>
-      <c r="J27" s="165"/>
-      <c r="K27" s="165"/>
-      <c r="L27" s="165"/>
-      <c r="M27" s="165"/>
-      <c r="N27" s="165"/>
-      <c r="O27" s="165"/>
-      <c r="P27" s="165"/>
-      <c r="Q27" s="165"/>
-      <c r="R27" s="165"/>
-      <c r="S27" s="166"/>
-    </row>
-    <row r="28" spans="1:20" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
-      <c r="P28" s="2"/>
-      <c r="Q28" s="2"/>
-      <c r="R28" s="2"/>
-      <c r="S28" s="2"/>
-    </row>
-    <row r="29" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="148" t="s">
+      <c r="D27" s="132"/>
+      <c r="E27" s="132"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="132"/>
+      <c r="H27" s="132"/>
+      <c r="I27" s="132"/>
+      <c r="J27" s="132"/>
+      <c r="K27" s="132"/>
+      <c r="L27" s="132"/>
+      <c r="M27" s="132"/>
+      <c r="N27" s="132"/>
+      <c r="O27" s="132"/>
+      <c r="P27" s="132"/>
+      <c r="Q27" s="132"/>
+      <c r="R27" s="132"/>
+      <c r="S27" s="132"/>
+      <c r="T27" s="132"/>
+      <c r="U27" s="133"/>
+    </row>
+    <row r="28" spans="3:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C28" s="134"/>
+      <c r="D28" s="135"/>
+      <c r="E28" s="135"/>
+      <c r="F28" s="135"/>
+      <c r="G28" s="135"/>
+      <c r="H28" s="135"/>
+      <c r="I28" s="135"/>
+      <c r="J28" s="135"/>
+      <c r="K28" s="135"/>
+      <c r="L28" s="135"/>
+      <c r="M28" s="135"/>
+      <c r="N28" s="135"/>
+      <c r="O28" s="135"/>
+      <c r="P28" s="135"/>
+      <c r="Q28" s="135"/>
+      <c r="R28" s="135"/>
+      <c r="S28" s="135"/>
+      <c r="T28" s="135"/>
+      <c r="U28" s="136"/>
+    </row>
+    <row r="29" spans="3:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+    </row>
+    <row r="30" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C30" s="105" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="79"/>
-      <c r="C29" s="79"/>
-      <c r="D29" s="79"/>
-      <c r="E29" s="79"/>
-      <c r="F29" s="79"/>
-      <c r="G29" s="79"/>
-      <c r="H29" s="79"/>
-      <c r="I29" s="79"/>
-      <c r="J29" s="79"/>
-      <c r="K29" s="79"/>
-      <c r="L29" s="79"/>
-      <c r="M29" s="79"/>
-      <c r="N29" s="79"/>
-      <c r="O29" s="79"/>
-      <c r="P29" s="79"/>
-      <c r="Q29" s="79"/>
-      <c r="R29" s="79"/>
-      <c r="S29" s="149"/>
-    </row>
-    <row r="30" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="167" t="s">
+      <c r="D30" s="106"/>
+      <c r="E30" s="106"/>
+      <c r="F30" s="106"/>
+      <c r="G30" s="106"/>
+      <c r="H30" s="106"/>
+      <c r="I30" s="106"/>
+      <c r="J30" s="106"/>
+      <c r="K30" s="106"/>
+      <c r="L30" s="106"/>
+      <c r="M30" s="106"/>
+      <c r="N30" s="106"/>
+      <c r="O30" s="106"/>
+      <c r="P30" s="106"/>
+      <c r="Q30" s="106"/>
+      <c r="R30" s="106"/>
+      <c r="S30" s="106"/>
+      <c r="T30" s="106"/>
+      <c r="U30" s="107"/>
+    </row>
+    <row r="31" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C31" s="137" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="170" t="s">
+      <c r="D31" s="140" t="s">
         <v>45</v>
       </c>
-      <c r="C30" s="173" t="s">
+      <c r="E31" s="121" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="91"/>
-      <c r="E30" s="174" t="s">
+      <c r="F31" s="116"/>
+      <c r="G31" s="146" t="s">
         <v>47</v>
       </c>
-      <c r="F30" s="175"/>
-      <c r="G30" s="175"/>
-      <c r="H30" s="175"/>
-      <c r="I30" s="176"/>
-      <c r="J30" s="183" t="s">
+      <c r="H31" s="147"/>
+      <c r="I31" s="147"/>
+      <c r="J31" s="147"/>
+      <c r="K31" s="148"/>
+      <c r="L31" s="155" t="s">
         <v>48</v>
       </c>
-      <c r="K30" s="184" t="s">
+      <c r="M31" s="115" t="s">
         <v>49</v>
       </c>
-      <c r="L30" s="91"/>
-      <c r="M30" s="101" t="s">
+      <c r="N31" s="116"/>
+      <c r="O31" s="126" t="s">
         <v>50</v>
       </c>
-      <c r="N30" s="84"/>
-      <c r="O30" s="84"/>
-      <c r="P30" s="84"/>
-      <c r="Q30" s="84"/>
-      <c r="R30" s="84"/>
-      <c r="S30" s="86"/>
-    </row>
-    <row r="31" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="168"/>
-      <c r="B31" s="171"/>
-      <c r="C31" s="153"/>
-      <c r="D31" s="74"/>
-      <c r="E31" s="177"/>
-      <c r="F31" s="178"/>
-      <c r="G31" s="178"/>
-      <c r="H31" s="178"/>
-      <c r="I31" s="179"/>
-      <c r="J31" s="171"/>
-      <c r="K31" s="153"/>
-      <c r="L31" s="74"/>
-      <c r="M31" s="18"/>
-      <c r="N31" s="19"/>
-      <c r="O31" s="20"/>
-      <c r="P31" s="18"/>
-      <c r="Q31" s="19"/>
-      <c r="R31" s="20"/>
-      <c r="S31" s="21"/>
-    </row>
-    <row r="32" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="168"/>
-      <c r="B32" s="171"/>
-      <c r="C32" s="153"/>
-      <c r="D32" s="74"/>
-      <c r="E32" s="177"/>
-      <c r="F32" s="178"/>
-      <c r="G32" s="178"/>
-      <c r="H32" s="178"/>
-      <c r="I32" s="179"/>
-      <c r="J32" s="171"/>
-      <c r="K32" s="153"/>
-      <c r="L32" s="74"/>
-      <c r="M32" s="18"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="20"/>
-      <c r="P32" s="18"/>
-      <c r="Q32" s="19"/>
-      <c r="R32" s="20"/>
-      <c r="S32" s="21"/>
-    </row>
-    <row r="33" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="168"/>
-      <c r="B33" s="171"/>
-      <c r="C33" s="153"/>
-      <c r="D33" s="74"/>
-      <c r="E33" s="177"/>
-      <c r="F33" s="178"/>
-      <c r="G33" s="178"/>
-      <c r="H33" s="178"/>
-      <c r="I33" s="179"/>
-      <c r="J33" s="171"/>
-      <c r="K33" s="153"/>
-      <c r="L33" s="74"/>
-      <c r="M33" s="18"/>
-      <c r="N33" s="19"/>
-      <c r="O33" s="20"/>
-      <c r="P33" s="18"/>
-      <c r="Q33" s="19"/>
-      <c r="R33" s="20"/>
-      <c r="S33" s="21"/>
-    </row>
-    <row r="34" spans="1:20" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="169"/>
-      <c r="B34" s="172"/>
-      <c r="C34" s="154"/>
-      <c r="D34" s="93"/>
-      <c r="E34" s="180"/>
-      <c r="F34" s="181"/>
-      <c r="G34" s="181"/>
-      <c r="H34" s="181"/>
-      <c r="I34" s="182"/>
-      <c r="J34" s="172"/>
-      <c r="K34" s="154"/>
-      <c r="L34" s="93"/>
-      <c r="M34" s="185" t="s">
+      <c r="P31" s="88"/>
+      <c r="Q31" s="88"/>
+      <c r="R31" s="88"/>
+      <c r="S31" s="88"/>
+      <c r="T31" s="88"/>
+      <c r="U31" s="92"/>
+    </row>
+    <row r="32" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C32" s="138"/>
+      <c r="D32" s="141"/>
+      <c r="E32" s="143"/>
+      <c r="F32" s="144"/>
+      <c r="G32" s="149"/>
+      <c r="H32" s="150"/>
+      <c r="I32" s="150"/>
+      <c r="J32" s="150"/>
+      <c r="K32" s="151"/>
+      <c r="L32" s="141"/>
+      <c r="M32" s="143"/>
+      <c r="N32" s="144"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="19"/>
+      <c r="Q32" s="20"/>
+      <c r="R32" s="18"/>
+      <c r="S32" s="19"/>
+      <c r="T32" s="20"/>
+      <c r="U32" s="21"/>
+    </row>
+    <row r="33" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C33" s="138"/>
+      <c r="D33" s="141"/>
+      <c r="E33" s="143"/>
+      <c r="F33" s="144"/>
+      <c r="G33" s="149"/>
+      <c r="H33" s="150"/>
+      <c r="I33" s="150"/>
+      <c r="J33" s="150"/>
+      <c r="K33" s="151"/>
+      <c r="L33" s="141"/>
+      <c r="M33" s="143"/>
+      <c r="N33" s="144"/>
+      <c r="O33" s="18"/>
+      <c r="P33" s="19"/>
+      <c r="Q33" s="20"/>
+      <c r="R33" s="18"/>
+      <c r="S33" s="19"/>
+      <c r="T33" s="20"/>
+      <c r="U33" s="21"/>
+    </row>
+    <row r="34" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C34" s="138"/>
+      <c r="D34" s="141"/>
+      <c r="E34" s="143"/>
+      <c r="F34" s="144"/>
+      <c r="G34" s="149"/>
+      <c r="H34" s="150"/>
+      <c r="I34" s="150"/>
+      <c r="J34" s="150"/>
+      <c r="K34" s="151"/>
+      <c r="L34" s="141"/>
+      <c r="M34" s="143"/>
+      <c r="N34" s="144"/>
+      <c r="O34" s="18"/>
+      <c r="P34" s="19"/>
+      <c r="Q34" s="20"/>
+      <c r="R34" s="18"/>
+      <c r="S34" s="19"/>
+      <c r="T34" s="20"/>
+      <c r="U34" s="21"/>
+    </row>
+    <row r="35" spans="3:22" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C35" s="139"/>
+      <c r="D35" s="142"/>
+      <c r="E35" s="145"/>
+      <c r="F35" s="110"/>
+      <c r="G35" s="152"/>
+      <c r="H35" s="153"/>
+      <c r="I35" s="153"/>
+      <c r="J35" s="153"/>
+      <c r="K35" s="154"/>
+      <c r="L35" s="142"/>
+      <c r="M35" s="145"/>
+      <c r="N35" s="110"/>
+      <c r="O35" s="156" t="s">
         <v>51</v>
       </c>
-      <c r="N34" s="93"/>
-      <c r="O34" s="22" t="s">
+      <c r="P35" s="110"/>
+      <c r="Q35" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="P34" s="156" t="s">
+      <c r="R35" s="130" t="s">
         <v>53</v>
       </c>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="23" t="s">
+      <c r="S35" s="110"/>
+      <c r="T35" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="S34" s="56" t="s">
+      <c r="U35" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="T34" s="14"/>
-    </row>
-    <row r="35" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="24" t="s">
+      <c r="V35" s="14"/>
+    </row>
+    <row r="36" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C36" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B35" s="9">
+      <c r="D36" s="9">
         <v>1</v>
       </c>
-      <c r="C35" s="157" t="s">
+      <c r="E36" s="124" t="s">
         <v>112</v>
       </c>
-      <c r="D35" s="158"/>
-      <c r="E35" s="25" t="s">
+      <c r="F36" s="128"/>
+      <c r="G36" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="F35" s="159" t="s">
+      <c r="H36" s="127" t="s">
         <v>84</v>
       </c>
-      <c r="G35" s="84"/>
-      <c r="H35" s="84"/>
-      <c r="I35" s="96"/>
-      <c r="J35" s="26" t="s">
+      <c r="I36" s="88"/>
+      <c r="J36" s="88"/>
+      <c r="K36" s="89"/>
+      <c r="L36" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="K35" s="160" t="s">
+      <c r="M36" s="129" t="s">
         <v>115</v>
       </c>
-      <c r="L35" s="96"/>
-      <c r="M35" s="101" t="s">
+      <c r="N36" s="89"/>
+      <c r="O36" s="126" t="s">
         <v>116</v>
       </c>
-      <c r="N35" s="96"/>
-      <c r="O35" s="9" t="s">
+      <c r="P36" s="89"/>
+      <c r="Q36" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="P35" s="101" t="s">
+      <c r="R36" s="126" t="s">
         <v>118</v>
       </c>
-      <c r="Q35" s="96"/>
-      <c r="R35" s="9" t="s">
+      <c r="S36" s="89"/>
+      <c r="T36" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="S35" s="57" t="s">
+      <c r="U36" s="57" t="s">
         <v>120</v>
       </c>
-      <c r="T35" s="14"/>
-    </row>
-    <row r="36" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="24" t="s">
+      <c r="V36" s="14"/>
+    </row>
+    <row r="37" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C37" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="9">
+      <c r="D37" s="9">
         <v>2</v>
       </c>
-      <c r="C36" s="157" t="s">
+      <c r="E37" s="124" t="s">
         <v>112</v>
       </c>
-      <c r="D36" s="158"/>
-      <c r="E36" s="25" t="s">
+      <c r="F37" s="128"/>
+      <c r="G37" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="F36" s="159" t="s">
+      <c r="H37" s="127" t="s">
         <v>84</v>
       </c>
-      <c r="G36" s="84"/>
-      <c r="H36" s="84"/>
-      <c r="I36" s="96"/>
-      <c r="J36" s="26" t="s">
+      <c r="I37" s="88"/>
+      <c r="J37" s="88"/>
+      <c r="K37" s="89"/>
+      <c r="L37" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="K36" s="160" t="s">
+      <c r="M37" s="129" t="s">
         <v>121</v>
       </c>
-      <c r="L36" s="96"/>
-      <c r="M36" s="101" t="s">
+      <c r="N37" s="89"/>
+      <c r="O37" s="126" t="s">
         <v>122</v>
       </c>
-      <c r="N36" s="96"/>
-      <c r="O36" s="9" t="s">
+      <c r="P37" s="89"/>
+      <c r="Q37" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="P36" s="101" t="s">
+      <c r="R37" s="126" t="s">
         <v>124</v>
       </c>
-      <c r="Q36" s="96"/>
-      <c r="R36" s="9" t="s">
+      <c r="S37" s="89"/>
+      <c r="T37" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="S36" s="57" t="s">
+      <c r="U37" s="57" t="s">
         <v>126</v>
       </c>
-      <c r="T36" s="14"/>
-    </row>
-    <row r="37" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="24" t="s">
+      <c r="V37" s="14"/>
+    </row>
+    <row r="38" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C38" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="9">
+      <c r="D38" s="9">
         <v>3</v>
       </c>
-      <c r="C37" s="157" t="s">
+      <c r="E38" s="124" t="s">
         <v>127</v>
       </c>
-      <c r="D37" s="158"/>
-      <c r="E37" s="28">
+      <c r="F38" s="128"/>
+      <c r="G38" s="28">
         <v>28</v>
       </c>
-      <c r="F37" s="159" t="s">
+      <c r="H38" s="127" t="s">
         <v>71</v>
       </c>
-      <c r="G37" s="84"/>
-      <c r="H37" s="84"/>
-      <c r="I37" s="96"/>
-      <c r="J37" s="26" t="s">
+      <c r="I38" s="88"/>
+      <c r="J38" s="88"/>
+      <c r="K38" s="89"/>
+      <c r="L38" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="K37" s="160" t="s">
+      <c r="M38" s="129" t="s">
         <v>129</v>
       </c>
-      <c r="L37" s="96"/>
-      <c r="M37" s="101" t="s">
+      <c r="N38" s="89"/>
+      <c r="O38" s="126" t="s">
         <v>130</v>
       </c>
-      <c r="N37" s="96"/>
-      <c r="O37" s="9" t="s">
+      <c r="P38" s="89"/>
+      <c r="Q38" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="P37" s="101" t="s">
+      <c r="R38" s="126" t="s">
         <v>132</v>
       </c>
-      <c r="Q37" s="96"/>
-      <c r="R37" s="9" t="s">
+      <c r="S38" s="89"/>
+      <c r="T38" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="S37" s="57" t="s">
+      <c r="U38" s="57" t="s">
         <v>142</v>
       </c>
-      <c r="T37" s="14"/>
-    </row>
-    <row r="38" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="24" t="s">
+      <c r="V38" s="14"/>
+    </row>
+    <row r="39" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C39" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="9">
+      <c r="D39" s="9">
         <v>4</v>
       </c>
-      <c r="C38" s="157" t="s">
+      <c r="E39" s="124" t="s">
         <v>127</v>
       </c>
-      <c r="D38" s="158"/>
-      <c r="E38" s="28">
+      <c r="F39" s="128"/>
+      <c r="G39" s="28">
         <v>28</v>
       </c>
-      <c r="F38" s="159" t="s">
+      <c r="H39" s="127" t="s">
         <v>71</v>
       </c>
-      <c r="G38" s="84"/>
-      <c r="H38" s="84"/>
-      <c r="I38" s="96"/>
-      <c r="J38" s="26" t="s">
+      <c r="I39" s="88"/>
+      <c r="J39" s="88"/>
+      <c r="K39" s="89"/>
+      <c r="L39" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="K38" s="160" t="s">
+      <c r="M39" s="129" t="s">
         <v>134</v>
       </c>
-      <c r="L38" s="96"/>
-      <c r="M38" s="101" t="s">
+      <c r="N39" s="89"/>
+      <c r="O39" s="126" t="s">
         <v>135</v>
       </c>
-      <c r="N38" s="96"/>
-      <c r="O38" s="9" t="s">
+      <c r="P39" s="89"/>
+      <c r="Q39" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="P38" s="101" t="s">
+      <c r="R39" s="126" t="s">
         <v>137</v>
       </c>
-      <c r="Q38" s="96"/>
-      <c r="R38" s="9" t="s">
+      <c r="S39" s="89"/>
+      <c r="T39" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="S38" s="57" t="s">
+      <c r="U39" s="57" t="s">
         <v>139</v>
       </c>
-      <c r="T38" s="14"/>
-    </row>
-    <row r="39" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="24" t="s">
+      <c r="V39" s="14"/>
+    </row>
+    <row r="40" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C40" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B39" s="9">
+      <c r="D40" s="9">
         <v>5</v>
       </c>
-      <c r="C39" s="157"/>
-      <c r="D39" s="96"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="159"/>
-      <c r="G39" s="84"/>
-      <c r="H39" s="84"/>
-      <c r="I39" s="96"/>
-      <c r="J39" s="26"/>
-      <c r="K39" s="186"/>
-      <c r="L39" s="96"/>
-      <c r="M39" s="101"/>
-      <c r="N39" s="96"/>
-      <c r="O39" s="9"/>
-      <c r="P39" s="101"/>
-      <c r="Q39" s="96"/>
-      <c r="R39" s="9"/>
-      <c r="S39" s="27"/>
-      <c r="T39" s="14"/>
-    </row>
-    <row r="40" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="24" t="s">
+      <c r="E40" s="124"/>
+      <c r="F40" s="89"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="127"/>
+      <c r="I40" s="88"/>
+      <c r="J40" s="88"/>
+      <c r="K40" s="89"/>
+      <c r="L40" s="26"/>
+      <c r="M40" s="90"/>
+      <c r="N40" s="89"/>
+      <c r="O40" s="126"/>
+      <c r="P40" s="89"/>
+      <c r="Q40" s="9"/>
+      <c r="R40" s="126"/>
+      <c r="S40" s="89"/>
+      <c r="T40" s="9"/>
+      <c r="U40" s="27"/>
+      <c r="V40" s="14"/>
+    </row>
+    <row r="41" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C41" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B40" s="9">
+      <c r="D41" s="9">
         <v>6</v>
       </c>
-      <c r="C40" s="157"/>
-      <c r="D40" s="96"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="159"/>
-      <c r="G40" s="84"/>
-      <c r="H40" s="84"/>
-      <c r="I40" s="96"/>
-      <c r="J40" s="26"/>
-      <c r="K40" s="186"/>
-      <c r="L40" s="96"/>
-      <c r="M40" s="101"/>
-      <c r="N40" s="96"/>
-      <c r="O40" s="9"/>
-      <c r="P40" s="101"/>
-      <c r="Q40" s="96"/>
-      <c r="R40" s="9"/>
-      <c r="S40" s="27"/>
-      <c r="T40" s="14"/>
-    </row>
-    <row r="41" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="24"/>
-      <c r="B41" s="9">
+      <c r="E41" s="124"/>
+      <c r="F41" s="89"/>
+      <c r="G41" s="28"/>
+      <c r="H41" s="127"/>
+      <c r="I41" s="88"/>
+      <c r="J41" s="88"/>
+      <c r="K41" s="89"/>
+      <c r="L41" s="26"/>
+      <c r="M41" s="90"/>
+      <c r="N41" s="89"/>
+      <c r="O41" s="126"/>
+      <c r="P41" s="89"/>
+      <c r="Q41" s="9"/>
+      <c r="R41" s="126"/>
+      <c r="S41" s="89"/>
+      <c r="T41" s="9"/>
+      <c r="U41" s="27"/>
+      <c r="V41" s="14"/>
+    </row>
+    <row r="42" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C42" s="24"/>
+      <c r="D42" s="9">
         <v>7</v>
       </c>
-      <c r="C41" s="157"/>
-      <c r="D41" s="96"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="159"/>
-      <c r="G41" s="84"/>
-      <c r="H41" s="84"/>
-      <c r="I41" s="96"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="186"/>
-      <c r="L41" s="96"/>
-      <c r="M41" s="101"/>
-      <c r="N41" s="96"/>
-      <c r="O41" s="9"/>
-      <c r="P41" s="101"/>
-      <c r="Q41" s="96"/>
-      <c r="R41" s="9"/>
-      <c r="S41" s="68"/>
-      <c r="T41" s="14"/>
-    </row>
-    <row r="42" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="29"/>
-      <c r="B42" s="55">
+      <c r="E42" s="124"/>
+      <c r="F42" s="89"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="127"/>
+      <c r="I42" s="88"/>
+      <c r="J42" s="88"/>
+      <c r="K42" s="89"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="90"/>
+      <c r="N42" s="89"/>
+      <c r="O42" s="126"/>
+      <c r="P42" s="89"/>
+      <c r="Q42" s="9"/>
+      <c r="R42" s="126"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="9"/>
+      <c r="U42" s="68"/>
+      <c r="V42" s="14"/>
+    </row>
+    <row r="43" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C43" s="29"/>
+      <c r="D43" s="55">
         <v>8</v>
       </c>
-      <c r="C42" s="187"/>
-      <c r="D42" s="91"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="188"/>
-      <c r="G42" s="139"/>
-      <c r="H42" s="139"/>
-      <c r="I42" s="91"/>
-      <c r="J42" s="31"/>
-      <c r="K42" s="189"/>
-      <c r="L42" s="91"/>
-      <c r="M42" s="173"/>
-      <c r="N42" s="91"/>
-      <c r="O42" s="55"/>
-      <c r="P42" s="173"/>
-      <c r="Q42" s="91"/>
-      <c r="R42" s="55"/>
-      <c r="S42" s="32"/>
-      <c r="T42" s="14"/>
-    </row>
-    <row r="43" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="190" t="s">
+      <c r="E43" s="118"/>
+      <c r="F43" s="116"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="119"/>
+      <c r="I43" s="102"/>
+      <c r="J43" s="102"/>
+      <c r="K43" s="116"/>
+      <c r="L43" s="31"/>
+      <c r="M43" s="120"/>
+      <c r="N43" s="116"/>
+      <c r="O43" s="121"/>
+      <c r="P43" s="116"/>
+      <c r="Q43" s="55"/>
+      <c r="R43" s="121"/>
+      <c r="S43" s="116"/>
+      <c r="T43" s="55"/>
+      <c r="U43" s="32"/>
+      <c r="V43" s="14"/>
+    </row>
+    <row r="44" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C44" s="122" t="s">
         <v>57</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="D44" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C43" s="157" t="s">
+      <c r="E44" s="124" t="s">
         <v>59</v>
       </c>
-      <c r="D43" s="84"/>
-      <c r="E43" s="84"/>
-      <c r="F43" s="84"/>
-      <c r="G43" s="84"/>
-      <c r="H43" s="84"/>
-      <c r="I43" s="84"/>
-      <c r="J43" s="96"/>
-      <c r="K43" s="191" t="s">
+      <c r="F44" s="88"/>
+      <c r="G44" s="88"/>
+      <c r="H44" s="88"/>
+      <c r="I44" s="88"/>
+      <c r="J44" s="88"/>
+      <c r="K44" s="88"/>
+      <c r="L44" s="89"/>
+      <c r="M44" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="L43" s="84"/>
-      <c r="M43" s="84"/>
-      <c r="N43" s="84"/>
-      <c r="O43" s="96"/>
-      <c r="P43" s="101" t="s">
+      <c r="N44" s="88"/>
+      <c r="O44" s="88"/>
+      <c r="P44" s="88"/>
+      <c r="Q44" s="89"/>
+      <c r="R44" s="126" t="s">
         <v>61</v>
       </c>
-      <c r="Q43" s="84"/>
-      <c r="R43" s="84"/>
-      <c r="S43" s="86"/>
-      <c r="T43" s="14"/>
-    </row>
-    <row r="44" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="72"/>
-      <c r="B44" s="33" t="s">
+      <c r="S44" s="88"/>
+      <c r="T44" s="88"/>
+      <c r="U44" s="92"/>
+      <c r="V44" s="14"/>
+    </row>
+    <row r="45" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C45" s="123"/>
+      <c r="D45" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="C44" s="184" t="s">
+      <c r="E45" s="115" t="s">
         <v>83</v>
       </c>
-      <c r="D44" s="139"/>
-      <c r="E44" s="139"/>
-      <c r="F44" s="139"/>
-      <c r="G44" s="139"/>
-      <c r="H44" s="139"/>
-      <c r="I44" s="139"/>
-      <c r="J44" s="91"/>
-      <c r="K44" s="186" t="s">
+      <c r="F45" s="102"/>
+      <c r="G45" s="102"/>
+      <c r="H45" s="102"/>
+      <c r="I45" s="102"/>
+      <c r="J45" s="102"/>
+      <c r="K45" s="102"/>
+      <c r="L45" s="116"/>
+      <c r="M45" s="90" t="s">
         <v>85</v>
       </c>
-      <c r="L44" s="84"/>
-      <c r="M44" s="84"/>
-      <c r="N44" s="84"/>
-      <c r="O44" s="96"/>
-      <c r="P44" s="186"/>
-      <c r="Q44" s="197"/>
-      <c r="R44" s="197"/>
-      <c r="S44" s="198"/>
-      <c r="T44" s="14"/>
-    </row>
-    <row r="45" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="72"/>
-      <c r="B45" s="33" t="s">
+      <c r="N45" s="88"/>
+      <c r="O45" s="88"/>
+      <c r="P45" s="88"/>
+      <c r="Q45" s="89"/>
+      <c r="R45" s="90"/>
+      <c r="S45" s="113"/>
+      <c r="T45" s="113"/>
+      <c r="U45" s="114"/>
+      <c r="V45" s="14"/>
+    </row>
+    <row r="46" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C46" s="123"/>
+      <c r="D46" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="C45" s="184" t="s">
+      <c r="E46" s="115" t="s">
         <v>70</v>
       </c>
-      <c r="D45" s="139"/>
-      <c r="E45" s="139"/>
-      <c r="F45" s="139"/>
-      <c r="G45" s="139"/>
-      <c r="H45" s="139"/>
-      <c r="I45" s="139"/>
-      <c r="J45" s="91"/>
-      <c r="K45" s="186" t="s">
+      <c r="F46" s="102"/>
+      <c r="G46" s="102"/>
+      <c r="H46" s="102"/>
+      <c r="I46" s="102"/>
+      <c r="J46" s="102"/>
+      <c r="K46" s="102"/>
+      <c r="L46" s="116"/>
+      <c r="M46" s="90" t="s">
         <v>86</v>
       </c>
-      <c r="L45" s="84"/>
-      <c r="M45" s="84"/>
-      <c r="N45" s="84"/>
-      <c r="O45" s="96"/>
-      <c r="P45" s="186"/>
-      <c r="Q45" s="197"/>
-      <c r="R45" s="197"/>
-      <c r="S45" s="198"/>
-      <c r="T45" s="14"/>
-    </row>
-    <row r="46" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="72"/>
-      <c r="B46" s="34" t="s">
+      <c r="N46" s="88"/>
+      <c r="O46" s="88"/>
+      <c r="P46" s="88"/>
+      <c r="Q46" s="89"/>
+      <c r="R46" s="90"/>
+      <c r="S46" s="113"/>
+      <c r="T46" s="113"/>
+      <c r="U46" s="114"/>
+      <c r="V46" s="14"/>
+    </row>
+    <row r="47" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C47" s="123"/>
+      <c r="D47" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="C46" s="184"/>
-      <c r="D46" s="139"/>
-      <c r="E46" s="139"/>
-      <c r="F46" s="139"/>
-      <c r="G46" s="139"/>
-      <c r="H46" s="139"/>
-      <c r="I46" s="139"/>
-      <c r="J46" s="91"/>
-      <c r="K46" s="199"/>
-      <c r="L46" s="139"/>
-      <c r="M46" s="139"/>
-      <c r="N46" s="139"/>
-      <c r="O46" s="91"/>
-      <c r="P46" s="199"/>
-      <c r="Q46" s="139"/>
-      <c r="R46" s="139"/>
-      <c r="S46" s="193"/>
-      <c r="T46" s="14"/>
-    </row>
-    <row r="47" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="192" t="s">
+      <c r="E47" s="115"/>
+      <c r="F47" s="102"/>
+      <c r="G47" s="102"/>
+      <c r="H47" s="102"/>
+      <c r="I47" s="102"/>
+      <c r="J47" s="102"/>
+      <c r="K47" s="102"/>
+      <c r="L47" s="116"/>
+      <c r="M47" s="117"/>
+      <c r="N47" s="102"/>
+      <c r="O47" s="102"/>
+      <c r="P47" s="102"/>
+      <c r="Q47" s="116"/>
+      <c r="R47" s="117"/>
+      <c r="S47" s="102"/>
+      <c r="T47" s="102"/>
+      <c r="U47" s="103"/>
+      <c r="V47" s="14"/>
+    </row>
+    <row r="48" spans="3:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C48" s="101" t="s">
         <v>88</v>
       </c>
-      <c r="B47" s="139"/>
-      <c r="C47" s="139"/>
-      <c r="D47" s="139"/>
-      <c r="E47" s="139"/>
-      <c r="F47" s="139"/>
-      <c r="G47" s="139"/>
-      <c r="H47" s="139"/>
-      <c r="I47" s="139"/>
-      <c r="J47" s="139"/>
-      <c r="K47" s="139"/>
-      <c r="L47" s="139"/>
-      <c r="M47" s="139"/>
-      <c r="N47" s="139"/>
-      <c r="O47" s="139"/>
-      <c r="P47" s="139"/>
-      <c r="Q47" s="139"/>
-      <c r="R47" s="139"/>
-      <c r="S47" s="193"/>
-    </row>
-    <row r="48" spans="1:20" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A48" s="75"/>
-      <c r="B48" s="76"/>
-      <c r="C48" s="76"/>
-      <c r="D48" s="76"/>
-      <c r="E48" s="76"/>
-      <c r="F48" s="76"/>
-      <c r="G48" s="76"/>
-      <c r="H48" s="76"/>
-      <c r="I48" s="76"/>
-      <c r="J48" s="76"/>
-      <c r="K48" s="76"/>
-      <c r="L48" s="76"/>
-      <c r="M48" s="76"/>
-      <c r="N48" s="76"/>
-      <c r="O48" s="76"/>
-      <c r="P48" s="76"/>
-      <c r="Q48" s="76"/>
-      <c r="R48" s="76"/>
-      <c r="S48" s="89"/>
-    </row>
-    <row r="49" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="148" t="s">
+      <c r="D48" s="102"/>
+      <c r="E48" s="102"/>
+      <c r="F48" s="102"/>
+      <c r="G48" s="102"/>
+      <c r="H48" s="102"/>
+      <c r="I48" s="102"/>
+      <c r="J48" s="102"/>
+      <c r="K48" s="102"/>
+      <c r="L48" s="102"/>
+      <c r="M48" s="102"/>
+      <c r="N48" s="102"/>
+      <c r="O48" s="102"/>
+      <c r="P48" s="102"/>
+      <c r="Q48" s="102"/>
+      <c r="R48" s="102"/>
+      <c r="S48" s="102"/>
+      <c r="T48" s="102"/>
+      <c r="U48" s="103"/>
+    </row>
+    <row r="49" spans="3:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C49" s="104"/>
+      <c r="D49" s="78"/>
+      <c r="E49" s="78"/>
+      <c r="F49" s="78"/>
+      <c r="G49" s="78"/>
+      <c r="H49" s="78"/>
+      <c r="I49" s="78"/>
+      <c r="J49" s="78"/>
+      <c r="K49" s="78"/>
+      <c r="L49" s="78"/>
+      <c r="M49" s="78"/>
+      <c r="N49" s="78"/>
+      <c r="O49" s="78"/>
+      <c r="P49" s="78"/>
+      <c r="Q49" s="78"/>
+      <c r="R49" s="78"/>
+      <c r="S49" s="78"/>
+      <c r="T49" s="78"/>
+      <c r="U49" s="86"/>
+    </row>
+    <row r="50" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C50" s="105" t="s">
         <v>64</v>
       </c>
-      <c r="B49" s="79"/>
-      <c r="C49" s="79"/>
-      <c r="D49" s="79"/>
-      <c r="E49" s="79"/>
-      <c r="F49" s="79"/>
-      <c r="G49" s="79"/>
-      <c r="H49" s="79"/>
-      <c r="I49" s="79"/>
-      <c r="J49" s="79"/>
-      <c r="K49" s="79"/>
-      <c r="L49" s="79"/>
-      <c r="M49" s="79"/>
-      <c r="N49" s="79"/>
-      <c r="O49" s="79"/>
-      <c r="P49" s="79"/>
-      <c r="Q49" s="79"/>
-      <c r="R49" s="79"/>
-      <c r="S49" s="149"/>
-      <c r="T49" s="14"/>
-    </row>
-    <row r="50" spans="1:20" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="194" t="s">
+      <c r="D50" s="106"/>
+      <c r="E50" s="106"/>
+      <c r="F50" s="106"/>
+      <c r="G50" s="106"/>
+      <c r="H50" s="106"/>
+      <c r="I50" s="106"/>
+      <c r="J50" s="106"/>
+      <c r="K50" s="106"/>
+      <c r="L50" s="106"/>
+      <c r="M50" s="106"/>
+      <c r="N50" s="106"/>
+      <c r="O50" s="106"/>
+      <c r="P50" s="106"/>
+      <c r="Q50" s="106"/>
+      <c r="R50" s="106"/>
+      <c r="S50" s="106"/>
+      <c r="T50" s="106"/>
+      <c r="U50" s="107"/>
+      <c r="V50" s="14"/>
+    </row>
+    <row r="51" spans="3:22" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C51" s="108" t="s">
         <v>65</v>
       </c>
-      <c r="B50" s="112"/>
-      <c r="C50" s="112"/>
-      <c r="D50" s="93"/>
-      <c r="E50" s="195" t="s">
+      <c r="D51" s="109"/>
+      <c r="E51" s="109"/>
+      <c r="F51" s="110"/>
+      <c r="G51" s="111" t="s">
         <v>47</v>
       </c>
-      <c r="F50" s="112"/>
-      <c r="G50" s="112"/>
-      <c r="H50" s="112"/>
-      <c r="I50" s="93"/>
-      <c r="J50" s="195" t="s">
+      <c r="H51" s="109"/>
+      <c r="I51" s="109"/>
+      <c r="J51" s="109"/>
+      <c r="K51" s="110"/>
+      <c r="L51" s="111" t="s">
         <v>66</v>
       </c>
-      <c r="K50" s="112"/>
-      <c r="L50" s="196"/>
-      <c r="M50" s="194" t="s">
+      <c r="M51" s="109"/>
+      <c r="N51" s="112"/>
+      <c r="O51" s="108" t="s">
         <v>65</v>
       </c>
-      <c r="N50" s="112"/>
-      <c r="O50" s="93"/>
-      <c r="P50" s="195" t="s">
+      <c r="P51" s="109"/>
+      <c r="Q51" s="110"/>
+      <c r="R51" s="111" t="s">
         <v>47</v>
       </c>
-      <c r="Q50" s="93"/>
-      <c r="R50" s="195" t="s">
+      <c r="S51" s="110"/>
+      <c r="T51" s="111" t="s">
         <v>66</v>
       </c>
-      <c r="S50" s="196"/>
-      <c r="T50" s="14"/>
-    </row>
-    <row r="51" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="213" t="s">
+      <c r="U51" s="112"/>
+      <c r="V51" s="14"/>
+    </row>
+    <row r="52" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C52" s="87" t="s">
         <v>112</v>
       </c>
-      <c r="B51" s="84"/>
-      <c r="C51" s="84"/>
-      <c r="D51" s="96"/>
-      <c r="E51" s="35" t="s">
+      <c r="D52" s="88"/>
+      <c r="E52" s="88"/>
+      <c r="F52" s="89"/>
+      <c r="G52" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="F51" s="186" t="str">
-        <f t="shared" ref="F51" si="0">F35</f>
+      <c r="H52" s="90" t="str">
+        <f t="shared" ref="H52" si="0">H36</f>
         <v>H</v>
       </c>
-      <c r="G51" s="84"/>
-      <c r="H51" s="84"/>
-      <c r="I51" s="96"/>
-      <c r="J51" s="214" t="s">
+      <c r="I52" s="88"/>
+      <c r="J52" s="88"/>
+      <c r="K52" s="89"/>
+      <c r="L52" s="91" t="s">
         <v>140</v>
       </c>
-      <c r="K51" s="84"/>
-      <c r="L51" s="86"/>
-      <c r="M51" s="213"/>
-      <c r="N51" s="84"/>
-      <c r="O51" s="96"/>
-      <c r="P51" s="33"/>
-      <c r="Q51" s="36"/>
-      <c r="R51" s="215"/>
-      <c r="S51" s="86"/>
-      <c r="T51" s="14"/>
-    </row>
-    <row r="52" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A52" s="216" t="s">
+      <c r="M52" s="88"/>
+      <c r="N52" s="92"/>
+      <c r="O52" s="87"/>
+      <c r="P52" s="88"/>
+      <c r="Q52" s="89"/>
+      <c r="R52" s="33"/>
+      <c r="S52" s="36"/>
+      <c r="T52" s="93"/>
+      <c r="U52" s="92"/>
+      <c r="V52" s="14"/>
+    </row>
+    <row r="53" spans="3:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C53" s="94" t="s">
         <v>127</v>
       </c>
-      <c r="B52" s="217"/>
-      <c r="C52" s="217"/>
-      <c r="D52" s="218"/>
-      <c r="E52" s="37">
-        <f t="shared" ref="E52:F52" si="1">E37</f>
+      <c r="D53" s="95"/>
+      <c r="E53" s="95"/>
+      <c r="F53" s="96"/>
+      <c r="G53" s="37">
+        <f t="shared" ref="G53:H53" si="1">G38</f>
         <v>28</v>
       </c>
-      <c r="F52" s="219" t="str">
+      <c r="H53" s="97" t="str">
         <f t="shared" si="1"/>
         <v>D</v>
       </c>
-      <c r="G52" s="217"/>
-      <c r="H52" s="217"/>
-      <c r="I52" s="218"/>
-      <c r="J52" s="220" t="s">
+      <c r="I53" s="95"/>
+      <c r="J53" s="95"/>
+      <c r="K53" s="96"/>
+      <c r="L53" s="98" t="s">
         <v>141</v>
       </c>
-      <c r="K52" s="217"/>
-      <c r="L52" s="221"/>
-      <c r="M52" s="216"/>
-      <c r="N52" s="217"/>
-      <c r="O52" s="218"/>
-      <c r="P52" s="37"/>
-      <c r="Q52" s="38"/>
-      <c r="R52" s="222"/>
-      <c r="S52" s="221"/>
-      <c r="T52" s="14"/>
-    </row>
-    <row r="53" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="200" t="s">
+      <c r="M53" s="95"/>
+      <c r="N53" s="99"/>
+      <c r="O53" s="94"/>
+      <c r="P53" s="95"/>
+      <c r="Q53" s="96"/>
+      <c r="R53" s="37"/>
+      <c r="S53" s="38"/>
+      <c r="T53" s="100"/>
+      <c r="U53" s="99"/>
+      <c r="V53" s="14"/>
+    </row>
+    <row r="54" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C54" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="B53" s="70"/>
-      <c r="C53" s="70"/>
-      <c r="D53" s="70"/>
-      <c r="E53" s="71"/>
-      <c r="F53" s="201" t="s">
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="71"/>
+      <c r="H54" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="G53" s="70"/>
-      <c r="H53" s="70"/>
-      <c r="I53" s="70"/>
-      <c r="J53" s="70"/>
-      <c r="K53" s="70"/>
-      <c r="L53" s="70"/>
-      <c r="M53" s="71"/>
-      <c r="N53" s="202" t="s">
+      <c r="I54" s="70"/>
+      <c r="J54" s="70"/>
+      <c r="K54" s="70"/>
+      <c r="L54" s="70"/>
+      <c r="M54" s="70"/>
+      <c r="N54" s="70"/>
+      <c r="O54" s="71"/>
+      <c r="P54" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="O53" s="203"/>
-      <c r="P53" s="203"/>
-      <c r="Q53" s="204"/>
-      <c r="R53" s="201" t="s">
+      <c r="Q54" s="74"/>
+      <c r="R54" s="74"/>
+      <c r="S54" s="75"/>
+      <c r="T54" s="72" t="s">
         <v>69</v>
       </c>
-      <c r="S53" s="205"/>
-      <c r="T53" s="14"/>
-    </row>
-    <row r="54" spans="1:20" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A54" s="206" t="s">
+      <c r="U54" s="76"/>
+      <c r="V54" s="14"/>
+    </row>
+    <row r="55" spans="3:22" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C55" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="B54" s="76"/>
-      <c r="C54" s="76"/>
-      <c r="D54" s="76"/>
-      <c r="E54" s="77"/>
-      <c r="F54" s="207" t="s">
+      <c r="D55" s="78"/>
+      <c r="E55" s="78"/>
+      <c r="F55" s="78"/>
+      <c r="G55" s="79"/>
+      <c r="H55" s="80" t="s">
         <v>74</v>
       </c>
-      <c r="G54" s="208"/>
-      <c r="H54" s="208"/>
-      <c r="I54" s="208"/>
-      <c r="J54" s="208"/>
-      <c r="K54" s="208"/>
-      <c r="L54" s="208"/>
-      <c r="M54" s="209"/>
-      <c r="N54" s="210"/>
-      <c r="O54" s="211"/>
-      <c r="P54" s="211"/>
-      <c r="Q54" s="212"/>
-      <c r="R54" s="210" t="s">
+      <c r="I55" s="81"/>
+      <c r="J55" s="81"/>
+      <c r="K55" s="81"/>
+      <c r="L55" s="81"/>
+      <c r="M55" s="81"/>
+      <c r="N55" s="81"/>
+      <c r="O55" s="82"/>
+      <c r="P55" s="83"/>
+      <c r="Q55" s="84"/>
+      <c r="R55" s="84"/>
+      <c r="S55" s="85"/>
+      <c r="T55" s="83" t="s">
         <v>127</v>
       </c>
-      <c r="S54" s="89"/>
-      <c r="T54" s="14"/>
-    </row>
-    <row r="55" spans="1:20" ht="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="56" spans="1:20" ht="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="57" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="58" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="59" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="60" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="61" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="62" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="63" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="64" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+      <c r="U55" s="86"/>
+      <c r="V55" s="14"/>
+    </row>
+    <row r="56" spans="3:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="57" spans="3:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="58" spans="3:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="59" spans="3:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="60" spans="3:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="61" spans="3:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="62" spans="3:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="63" spans="3:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="64" spans="3:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -4331,175 +4333,176 @@
     <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="146">
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="F53:M53"/>
-    <mergeCell ref="N53:Q53"/>
-    <mergeCell ref="R53:S53"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="F54:M54"/>
-    <mergeCell ref="N54:Q54"/>
-    <mergeCell ref="R54:S54"/>
-    <mergeCell ref="A51:D51"/>
-    <mergeCell ref="F51:I51"/>
-    <mergeCell ref="J51:L51"/>
-    <mergeCell ref="M51:O51"/>
+    <mergeCell ref="C2:F4"/>
+    <mergeCell ref="G2:Q2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:U3"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J4:U4"/>
+    <mergeCell ref="C9:D10"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="R9:U9"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="O10:S10"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="C6:U6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:K8"/>
+    <mergeCell ref="R8:U8"/>
+    <mergeCell ref="D11:K11"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="S11:U11"/>
+    <mergeCell ref="D12:U12"/>
+    <mergeCell ref="C14:U14"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="H15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="H16:N16"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="Q16:T16"/>
+    <mergeCell ref="C17:D18"/>
+    <mergeCell ref="G17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="Q17:U17"/>
+    <mergeCell ref="G18:L18"/>
+    <mergeCell ref="G23:N23"/>
+    <mergeCell ref="O23:U24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:N24"/>
+    <mergeCell ref="C26:U26"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="C19:N19"/>
+    <mergeCell ref="O19:U21"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="Q22:U22"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="H36:K36"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C27:U28"/>
+    <mergeCell ref="C30:U30"/>
+    <mergeCell ref="C31:C35"/>
+    <mergeCell ref="D31:D35"/>
+    <mergeCell ref="E31:F35"/>
+    <mergeCell ref="G31:K35"/>
+    <mergeCell ref="L31:L35"/>
+    <mergeCell ref="M31:N35"/>
+    <mergeCell ref="O31:U31"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="H38:K38"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="H39:K39"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="H40:K40"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="M41:N41"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="H42:K42"/>
+    <mergeCell ref="M42:N42"/>
+    <mergeCell ref="O42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="H43:K43"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="O43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C44:C47"/>
+    <mergeCell ref="E44:L44"/>
+    <mergeCell ref="M44:Q44"/>
+    <mergeCell ref="R44:U44"/>
+    <mergeCell ref="E45:L45"/>
+    <mergeCell ref="C48:U49"/>
+    <mergeCell ref="C50:U50"/>
+    <mergeCell ref="C51:F51"/>
+    <mergeCell ref="G51:K51"/>
+    <mergeCell ref="L51:N51"/>
+    <mergeCell ref="O51:Q51"/>
     <mergeCell ref="R51:S51"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="J52:L52"/>
-    <mergeCell ref="M52:O52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="A47:S48"/>
-    <mergeCell ref="A49:S49"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="E50:I50"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="M50:O50"/>
-    <mergeCell ref="P50:Q50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="K44:O44"/>
-    <mergeCell ref="P44:S44"/>
-    <mergeCell ref="C45:J45"/>
-    <mergeCell ref="K45:O45"/>
-    <mergeCell ref="P45:S45"/>
-    <mergeCell ref="C46:J46"/>
-    <mergeCell ref="K46:O46"/>
-    <mergeCell ref="P46:S46"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="F42:I42"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="M42:N42"/>
-    <mergeCell ref="P42:Q42"/>
-    <mergeCell ref="A43:A46"/>
-    <mergeCell ref="C43:J43"/>
-    <mergeCell ref="K43:O43"/>
-    <mergeCell ref="P43:S43"/>
-    <mergeCell ref="C44:J44"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="P40:Q40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:I41"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="M41:N41"/>
-    <mergeCell ref="P41:Q41"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="P38:Q38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="P39:Q39"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F36:I36"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="P36:Q36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="P37:Q37"/>
-    <mergeCell ref="P34:Q34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="A26:S27"/>
-    <mergeCell ref="A29:S29"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="B30:B34"/>
-    <mergeCell ref="C30:D34"/>
-    <mergeCell ref="E30:I34"/>
-    <mergeCell ref="J30:J34"/>
-    <mergeCell ref="K30:L34"/>
-    <mergeCell ref="M30:S30"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="E22:L22"/>
-    <mergeCell ref="M22:S23"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:L23"/>
-    <mergeCell ref="A25:S25"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="A18:L18"/>
-    <mergeCell ref="M18:S20"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="O21:S21"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="F15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="O15:R15"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="E16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="O16:S16"/>
-    <mergeCell ref="E17:J17"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="B11:S11"/>
-    <mergeCell ref="A13:S13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="A1:D3"/>
-    <mergeCell ref="E1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:S2"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:S3"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="P8:S8"/>
-    <mergeCell ref="E9:J9"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="M9:Q9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="A5:S5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:I6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:I7"/>
-    <mergeCell ref="P7:S7"/>
+    <mergeCell ref="T51:U51"/>
+    <mergeCell ref="M45:Q45"/>
+    <mergeCell ref="R45:U45"/>
+    <mergeCell ref="E46:L46"/>
+    <mergeCell ref="M46:Q46"/>
+    <mergeCell ref="R46:U46"/>
+    <mergeCell ref="E47:L47"/>
+    <mergeCell ref="M47:Q47"/>
+    <mergeCell ref="R47:U47"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="H54:O54"/>
+    <mergeCell ref="P54:S54"/>
+    <mergeCell ref="T54:U54"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="H55:O55"/>
+    <mergeCell ref="P55:S55"/>
+    <mergeCell ref="T55:U55"/>
+    <mergeCell ref="C52:F52"/>
+    <mergeCell ref="H52:K52"/>
+    <mergeCell ref="L52:N52"/>
+    <mergeCell ref="O52:Q52"/>
+    <mergeCell ref="T52:U52"/>
+    <mergeCell ref="C53:F53"/>
+    <mergeCell ref="H53:K53"/>
+    <mergeCell ref="L53:N53"/>
+    <mergeCell ref="O53:Q53"/>
+    <mergeCell ref="T53:U53"/>
   </mergeCells>
-  <conditionalFormatting sqref="C16:C17">
+  <conditionalFormatting sqref="E17:E18">
     <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E16:J17">
+  <conditionalFormatting sqref="G17:L18">
     <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M35:S38">
+  <conditionalFormatting sqref="O36:U39">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.78740157480314965" right="0" top="0.78740157480314965" bottom="0.19685039370078741" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="77" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="73" orientation="portrait" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
-    <brk id="19" max="1048575" man="1"/>
+    <brk id="21" max="1048575" man="1"/>
   </colBreaks>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -4515,6 +4518,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4f78bd75-e5af-473e-a771-af58d935aeec">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <teste xmlns="4f78bd75-e5af-473e-a771-af58d935aeec" xsi:nil="true"/>
+    <TaxCatchAll xmlns="2e1cb776-6995-4ef2-a2af-ac4d4b6f4925" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010064F60118CF4DD941A5203D2B469A8CE2" ma:contentTypeVersion="20" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="d9d0e163e276c1657cd95225610b57db">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4f78bd75-e5af-473e-a771-af58d935aeec" xmlns:ns3="2e1cb776-6995-4ef2-a2af-ac4d4b6f4925" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8369f36d4fda10f60ea49ea02112d021" ns2:_="" ns3:_="">
     <xsd:import namespace="4f78bd75-e5af-473e-a771-af58d935aeec"/>
@@ -4783,18 +4798,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4f78bd75-e5af-473e-a771-af58d935aeec">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <teste xmlns="4f78bd75-e5af-473e-a771-af58d935aeec" xsi:nil="true"/>
-    <TaxCatchAll xmlns="2e1cb776-6995-4ef2-a2af-ac4d4b6f4925" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02FE57D6-0C16-43C0-88C7-70BAEB9EB740}">
   <ds:schemaRefs>
@@ -4804,6 +4807,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FABCB45-9310-4EAF-865B-FCDA80FA346B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4f78bd75-e5af-473e-a771-af58d935aeec"/>
+    <ds:schemaRef ds:uri="2e1cb776-6995-4ef2-a2af-ac4d4b6f4925"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E93A1539-E86C-43FA-B071-A818CB2C811D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4820,15 +4834,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FABCB45-9310-4EAF-865B-FCDA80FA346B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4f78bd75-e5af-473e-a771-af58d935aeec"/>
-    <ds:schemaRef ds:uri="2e1cb776-6995-4ef2-a2af-ac4d4b6f4925"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>